--- a/research/results/paper_forward_5y.xlsx
+++ b/research/results/paper_forward_5y.xlsx
@@ -57,7 +57,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,6 +103,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -464,10 +470,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -480,12 +486,13 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2026 年(全 42 セル)</t>
+          <t>紙上フォワード 月次リターン 2026 年(全 47 セル = 既存 42 + 候補 5)</t>
         </is>
       </c>
     </row>
@@ -562,6 +569,11 @@
           <t>活動月数</t>
         </is>
       </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>+月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -607,6 +619,9 @@
       <c r="M5" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N5" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -652,6 +667,9 @@
       <c r="M6" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -697,6 +715,9 @@
       <c r="M7" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N7" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -742,6 +763,9 @@
       <c r="M8" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N8" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -787,6 +811,9 @@
       <c r="M9" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N9" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -832,6 +859,9 @@
       <c r="M10" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N10" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -877,6 +907,9 @@
       <c r="M11" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N11" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -919,6 +952,9 @@
       <c r="M12" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="N12" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -961,6 +997,9 @@
       <c r="M13" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="N13" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1006,6 +1045,9 @@
       <c r="M14" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N14" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1051,6 +1093,9 @@
       <c r="M15" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N15" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1096,6 +1141,9 @@
       <c r="M16" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N16" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1141,6 +1189,9 @@
       <c r="M17" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N17" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1186,6 +1237,9 @@
       <c r="M18" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N18" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1231,6 +1285,9 @@
       <c r="M19" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N19" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1276,6 +1333,9 @@
       <c r="M20" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N20" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1321,6 +1381,9 @@
       <c r="M21" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N21" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1366,6 +1429,9 @@
       <c r="M22" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N22" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1411,6 +1477,9 @@
       <c r="M23" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N23" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1456,6 +1525,9 @@
       <c r="M24" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N24" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1501,6 +1573,9 @@
       <c r="M25" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N25" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1546,6 +1621,9 @@
       <c r="M26" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N26" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1591,6 +1669,9 @@
       <c r="M27" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N27" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1636,6 +1717,9 @@
       <c r="M28" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N28" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1681,6 +1765,9 @@
       <c r="M29" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N29" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1708,6 +1795,9 @@
       <c r="M30" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="N30" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1735,6 +1825,9 @@
       <c r="M31" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="N31" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1762,6 +1855,9 @@
       <c r="M32" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="N32" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1792,6 +1888,9 @@
       <c r="M33" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="N33" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1822,6 +1921,9 @@
       <c r="M34" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="N34" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1843,6 +1945,9 @@
       <c r="M35" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="N35" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1876,6 +1981,9 @@
       <c r="M36" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="N36" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1897,6 +2005,9 @@
       <c r="M37" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1930,6 +2041,9 @@
       <c r="M38" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="N38" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1975,6 +2089,9 @@
       <c r="M39" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N39" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -2020,6 +2137,9 @@
       <c r="M40" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N40" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2065,6 +2185,9 @@
       <c r="M41" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N41" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2110,6 +2233,9 @@
       <c r="M42" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N42" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2155,6 +2281,9 @@
       <c r="M43" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N43" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2197,6 +2326,9 @@
       <c r="M44" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="N44" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2242,6 +2374,9 @@
       <c r="M45" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N45" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2287,30 +2422,273 @@
       <c r="M46" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="N46" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MonS(候補)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.008239999999999999</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.00422</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.00834</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.00303</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.00731</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>0.04141946271644414</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(Python で計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>FriS(候補)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>-0.01551</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.03045</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>-0.00644</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>-0.006979999999999999</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>-0.00075</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>0.04335460053358542</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。それ以前は選抜がこの期間を見て決めた値なので、手法の証拠にはならない。</t>
-        </is>
+          <t>WedS(候補)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>-0.01076</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-0.00745</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-0.006690000000000001</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>-0.00369</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>-0.007353600419141348</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>TueS(候補)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.01317</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.00615</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.00477</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.00102</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.00604</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>0.00194</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>-0.00333</v>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>0.01142939288236544</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Thu(候補)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>-0.06426</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-0.03804</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-0.01259</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.00094</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.01981</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>-0.01494</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>-0.01183</v>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>-0.0648644976425542</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:K46">
+  <conditionalFormatting sqref="C5:K51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -2332,10 +2710,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -2351,12 +2729,13 @@
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2025 年(全 42 セル)</t>
+          <t>紙上フォワード 月次リターン 2025 年(全 47 セル = 既存 42 + 候補 5)</t>
         </is>
       </c>
     </row>
@@ -2448,6 +2827,11 @@
           <t>活動月数</t>
         </is>
       </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>+月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2502,6 +2886,9 @@
       <c r="P5" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q5" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2556,6 +2943,9 @@
       <c r="P6" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q6" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2610,6 +3000,9 @@
       <c r="P7" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q7" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2664,6 +3057,9 @@
       <c r="P8" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q8" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2718,6 +3114,9 @@
       <c r="P9" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q9" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2772,6 +3171,9 @@
       <c r="P10" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q10" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2826,6 +3228,9 @@
       <c r="P11" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q11" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2880,6 +3285,9 @@
       <c r="P12" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q12" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2934,6 +3342,9 @@
       <c r="P13" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q13" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2988,6 +3399,9 @@
       <c r="P14" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q14" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3042,6 +3456,9 @@
       <c r="P15" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q15" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3096,6 +3513,9 @@
       <c r="P16" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q16" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3150,6 +3570,9 @@
       <c r="P17" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q17" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3204,6 +3627,9 @@
       <c r="P18" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q18" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3258,6 +3684,9 @@
       <c r="P19" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q19" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3312,6 +3741,9 @@
       <c r="P20" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q20" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3366,6 +3798,9 @@
       <c r="P21" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q21" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3420,6 +3855,9 @@
       <c r="P22" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q22" s="4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3474,6 +3912,9 @@
       <c r="P23" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q23" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3528,6 +3969,9 @@
       <c r="P24" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q24" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3582,6 +4026,9 @@
       <c r="P25" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q25" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3636,6 +4083,9 @@
       <c r="P26" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q26" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3690,6 +4140,9 @@
       <c r="P27" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q27" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3744,6 +4197,9 @@
       <c r="P28" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q28" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3798,6 +4254,9 @@
       <c r="P29" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q29" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3831,6 +4290,9 @@
       <c r="P30" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="Q30" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3867,6 +4329,9 @@
       <c r="P31" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q31" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -3906,6 +4371,9 @@
       <c r="P32" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q32" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3930,6 +4398,9 @@
       <c r="P33" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="Q33" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3957,6 +4428,9 @@
       <c r="P34" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="Q34" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3984,6 +4458,9 @@
       <c r="P35" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="Q35" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4023,6 +4500,9 @@
       <c r="P36" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q36" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4059,6 +4539,9 @@
       <c r="P37" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q37" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4092,6 +4575,9 @@
       <c r="P38" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="Q38" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4146,6 +4632,9 @@
       <c r="P39" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q39" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4200,6 +4689,9 @@
       <c r="P40" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q40" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4254,6 +4746,9 @@
       <c r="P41" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q41" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4308,6 +4803,9 @@
       <c r="P42" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q42" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -4362,6 +4860,9 @@
       <c r="P43" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q43" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4401,6 +4902,9 @@
       <c r="P44" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q44" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -4455,6 +4959,9 @@
       <c r="P45" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q45" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4509,30 +5016,318 @@
       <c r="P46" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q46" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MonS(候補)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.00205</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.00508</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.00532</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.00661</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.00727</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.0005899999999999999</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.006959999999999999</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.00466</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.0007099999999999999</v>
+      </c>
+      <c r="O47" s="7" t="n">
+        <v>0.04413556239882821</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(Python で計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>FriS(候補)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.00394</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.03224</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.02547</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.01047</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>-0.00616</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0.00473</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0.06177474295146523</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。それ以前は選抜がこの期間を見て決めた値なので、手法の証拠にはならない。</t>
-        </is>
+          <t>WedS(候補)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.00061</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.008619999999999999</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-0.005759999999999999</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-0.02502</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.00506</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.00324</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.004670000000000001</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-0.005390000000000001</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <v>0.003486457152248157</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>TueS(候補)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.00309</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.00167</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.01268</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0.005719999999999999</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0.00818</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>-0.00231</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>-0.0003500000000000001</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0.01381183747722514</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Thu(候補)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.03668</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>-0.01188</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.02773</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.03561</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.00506</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.00595</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-0.00086</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.02009</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.05052</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>-0.01719</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>0.1899693158941536</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N46">
+  <conditionalFormatting sqref="C5:N51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -4554,10 +5349,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -4573,12 +5368,13 @@
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2024 年(全 42 セル)</t>
+          <t>紙上フォワード 月次リターン 2024 年(全 47 セル = 既存 42 + 候補 5)</t>
         </is>
       </c>
     </row>
@@ -4670,6 +5466,11 @@
           <t>活動月数</t>
         </is>
       </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>+月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4724,6 +5525,9 @@
       <c r="P5" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q5" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4778,6 +5582,9 @@
       <c r="P6" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q6" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4832,6 +5639,9 @@
       <c r="P7" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q7" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -4886,6 +5696,9 @@
       <c r="P8" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q8" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4940,6 +5753,9 @@
       <c r="P9" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q9" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -4994,6 +5810,9 @@
       <c r="P10" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q10" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -5048,6 +5867,9 @@
       <c r="P11" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q11" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -5102,6 +5924,9 @@
       <c r="P12" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q12" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -5156,6 +5981,9 @@
       <c r="P13" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q13" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -5210,6 +6038,9 @@
       <c r="P14" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q14" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -5264,6 +6095,9 @@
       <c r="P15" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q15" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -5318,6 +6152,9 @@
       <c r="P16" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q16" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -5372,6 +6209,9 @@
       <c r="P17" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q17" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -5426,6 +6266,9 @@
       <c r="P18" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q18" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -5480,6 +6323,9 @@
       <c r="P19" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q19" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5534,6 +6380,9 @@
       <c r="P20" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q20" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -5588,6 +6437,9 @@
       <c r="P21" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q21" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -5642,6 +6494,9 @@
       <c r="P22" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q22" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -5696,6 +6551,9 @@
       <c r="P23" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q23" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -5750,6 +6608,9 @@
       <c r="P24" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q24" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -5804,6 +6665,9 @@
       <c r="P25" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q25" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -5858,6 +6722,9 @@
       <c r="P26" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q26" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -5912,6 +6779,9 @@
       <c r="P27" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q27" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -5966,6 +6836,9 @@
       <c r="P28" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q28" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -6020,6 +6893,9 @@
       <c r="P29" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q29" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -6044,6 +6920,9 @@
       <c r="P30" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="Q30" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -6080,6 +6959,9 @@
       <c r="P31" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q31" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -6125,6 +7007,9 @@
       <c r="P32" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="Q32" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -6161,6 +7046,9 @@
       <c r="P33" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q33" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -6200,6 +7088,9 @@
       <c r="P34" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q34" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -6221,6 +7112,9 @@
       <c r="P35" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Q35" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -6254,6 +7148,9 @@
       <c r="P36" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="Q36" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -6290,6 +7187,9 @@
       <c r="P37" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q37" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -6335,6 +7235,9 @@
       <c r="P38" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="Q38" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -6389,6 +7292,9 @@
       <c r="P39" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q39" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -6443,6 +7349,9 @@
       <c r="P40" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q40" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -6497,6 +7406,9 @@
       <c r="P41" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q41" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -6551,6 +7463,9 @@
       <c r="P42" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q42" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -6605,6 +7520,9 @@
       <c r="P43" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q43" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -6644,6 +7562,9 @@
       <c r="P44" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q44" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -6698,6 +7619,9 @@
       <c r="P45" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q45" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -6752,30 +7676,318 @@
       <c r="P46" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q46" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MonS(候補)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.00436</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>-0.00342</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.005620000000000001</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>-0.00092</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.006889999999999999</v>
+      </c>
+      <c r="O47" s="7" t="n">
+        <v>0.02677412663811274</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(Python で計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>FriS(候補)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.00559</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.01206</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.01399</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.01936</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.02186</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0.00353</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0.00198</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0.05097233751048691</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。それ以前は選抜がこの期間を見て決めた値なので、手法の証拠にはならない。</t>
-        </is>
+          <t>WedS(候補)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.01775</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>-0.00183</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.00149</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.02143</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>-0.01226</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>-0.00526</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <v>0.008285637998122874</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>TueS(候補)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>-0.009769999999999999</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.00017</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.00204</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.00258</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0.00249</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.00715</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>-0.00532</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>-0.00112</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0.01956336461375163</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Thu(候補)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.01318</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.01418</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.01405</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.02761</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0005600000000000001</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.01429</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>-0.02198</v>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>0.1529835924083394</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N46">
+  <conditionalFormatting sqref="C5:N51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -6797,10 +8009,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -6816,12 +8028,13 @@
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2023 年(全 42 セル)</t>
+          <t>紙上フォワード 月次リターン 2023 年(全 47 セル = 既存 42 + 候補 5)</t>
         </is>
       </c>
     </row>
@@ -6913,6 +8126,11 @@
           <t>活動月数</t>
         </is>
       </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>+月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6967,6 +8185,9 @@
       <c r="P5" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q5" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7021,6 +8242,9 @@
       <c r="P6" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q6" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7075,6 +8299,9 @@
       <c r="P7" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q7" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -7129,6 +8356,9 @@
       <c r="P8" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q8" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7183,6 +8413,9 @@
       <c r="P9" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q9" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -7237,6 +8470,9 @@
       <c r="P10" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q10" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -7291,6 +8527,9 @@
       <c r="P11" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q11" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -7345,6 +8584,9 @@
       <c r="P12" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q12" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -7399,6 +8641,9 @@
       <c r="P13" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q13" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -7453,6 +8698,9 @@
       <c r="P14" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q14" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -7507,6 +8755,9 @@
       <c r="P15" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q15" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7561,6 +8812,9 @@
       <c r="P16" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q16" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -7615,6 +8869,9 @@
       <c r="P17" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q17" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -7669,6 +8926,9 @@
       <c r="P18" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q18" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7723,6 +8983,9 @@
       <c r="P19" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q19" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7777,6 +9040,9 @@
       <c r="P20" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q20" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -7831,6 +9097,9 @@
       <c r="P21" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q21" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -7885,6 +9154,9 @@
       <c r="P22" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q22" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7939,6 +9211,9 @@
       <c r="P23" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q23" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -7993,6 +9268,9 @@
       <c r="P24" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q24" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -8047,6 +9325,9 @@
       <c r="P25" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q25" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -8101,6 +9382,9 @@
       <c r="P26" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q26" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -8155,6 +9439,9 @@
       <c r="P27" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q27" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -8209,6 +9496,9 @@
       <c r="P28" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q28" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -8263,6 +9553,9 @@
       <c r="P29" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q29" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -8299,6 +9592,9 @@
       <c r="P30" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q30" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -8338,6 +9634,9 @@
       <c r="P31" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q31" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -8374,6 +9673,9 @@
       <c r="P32" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q32" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -8416,6 +9718,9 @@
       <c r="P33" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="Q33" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -8446,6 +9751,9 @@
       <c r="P34" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="Q34" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -8473,6 +9781,9 @@
       <c r="P35" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="Q35" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -8509,6 +9820,9 @@
       <c r="P36" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q36" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -8542,6 +9856,9 @@
       <c r="P37" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="Q37" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -8581,6 +9898,9 @@
       <c r="P38" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q38" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -8635,6 +9955,9 @@
       <c r="P39" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q39" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -8689,6 +10012,9 @@
       <c r="P40" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q40" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -8743,6 +10069,9 @@
       <c r="P41" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q41" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -8797,6 +10126,9 @@
       <c r="P42" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q42" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -8851,6 +10183,9 @@
       <c r="P43" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q43" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -8899,6 +10234,9 @@
       <c r="P44" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="Q44" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -8953,6 +10291,9 @@
       <c r="P45" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q45" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -9007,30 +10348,318 @@
       <c r="P46" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q46" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MonS(候補)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>-0.00834</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.00461</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.00454</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.008960000000000001</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.00483</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.00514</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>-0.00736</v>
+      </c>
+      <c r="O47" s="7" t="n">
+        <v>0.01479958714890284</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(Python で計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>FriS(候補)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>-0.03353</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.03909</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-0.00478</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.01759</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>-0.00784</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>-0.005330000000000001</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>-0.02624</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>-0.00282</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0.006978775912764412</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。それ以前は選抜がこの期間を見て決めた値なので、手法の証拠にはならない。</t>
-        </is>
+          <t>WedS(候補)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.00493</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-0.00156</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.00165</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>-0.00993</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.01959</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <v>0.09996827109187167</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>TueS(候補)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>-0.00707</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.00451</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.00078</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0.00984</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0.00895</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0.00049</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0.05430363939761329</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Thu(候補)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>-0.00289</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-0.00248</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.00577</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-0.00641</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-0.00359</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>0.00713</v>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>0.04411989493204782</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N46">
+  <conditionalFormatting sqref="C5:N51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9052,10 +10681,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -9071,12 +10700,13 @@
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2022 年(全 42 セル)</t>
+          <t>紙上フォワード 月次リターン 2022 年(全 47 セル = 既存 42 + 候補 5)</t>
         </is>
       </c>
     </row>
@@ -9168,6 +10798,11 @@
           <t>活動月数</t>
         </is>
       </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>+月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -9222,6 +10857,9 @@
       <c r="P5" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q5" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -9276,6 +10914,9 @@
       <c r="P6" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q6" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -9330,6 +10971,9 @@
       <c r="P7" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q7" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -9384,6 +11028,9 @@
       <c r="P8" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q8" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -9438,6 +11085,9 @@
       <c r="P9" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q9" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -9492,6 +11142,9 @@
       <c r="P10" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q10" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9546,6 +11199,9 @@
       <c r="P11" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q11" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -9600,6 +11256,9 @@
       <c r="P12" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q12" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -9654,6 +11313,9 @@
       <c r="P13" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q13" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -9708,6 +11370,9 @@
       <c r="P14" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q14" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -9762,6 +11427,9 @@
       <c r="P15" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q15" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -9816,6 +11484,9 @@
       <c r="P16" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q16" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -9870,6 +11541,9 @@
       <c r="P17" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q17" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -9924,6 +11598,9 @@
       <c r="P18" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q18" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -9978,6 +11655,9 @@
       <c r="P19" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q19" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10032,6 +11712,9 @@
       <c r="P20" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q20" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -10086,6 +11769,9 @@
       <c r="P21" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q21" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10140,6 +11826,9 @@
       <c r="P22" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q22" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -10194,6 +11883,9 @@
       <c r="P23" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q23" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10248,6 +11940,9 @@
       <c r="P24" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q24" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -10302,6 +11997,9 @@
       <c r="P25" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q25" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10356,6 +12054,9 @@
       <c r="P26" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q26" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -10410,6 +12111,9 @@
       <c r="P27" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q27" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -10464,6 +12168,9 @@
       <c r="P28" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q28" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -10518,6 +12225,9 @@
       <c r="P29" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q29" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -10563,6 +12273,9 @@
       <c r="P30" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="Q30" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -10605,6 +12318,9 @@
       <c r="P31" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="Q31" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -10644,6 +12360,9 @@
       <c r="P32" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q32" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -10683,6 +12402,9 @@
       <c r="P33" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q33" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -10722,6 +12444,9 @@
       <c r="P34" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="Q34" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -10743,6 +12468,9 @@
       <c r="P35" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Q35" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -10788,6 +12516,9 @@
       <c r="P36" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="Q36" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -10824,6 +12555,9 @@
       <c r="P37" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="Q37" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -10857,6 +12591,9 @@
       <c r="P38" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="Q38" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -10911,6 +12648,9 @@
       <c r="P39" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q39" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -10965,6 +12705,9 @@
       <c r="P40" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q40" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -11019,6 +12762,9 @@
       <c r="P41" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q41" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -11073,6 +12819,9 @@
       <c r="P42" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q42" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -11127,6 +12876,9 @@
       <c r="P43" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q43" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -11169,6 +12921,9 @@
       <c r="P44" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="Q44" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -11223,6 +12978,9 @@
       <c r="P45" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q45" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -11277,30 +13035,318 @@
       <c r="P46" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="Q46" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MonS(候補)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>-0.00351</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.006690000000000001</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>-0.01342</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.009649999999999999</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.01016</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.00019</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.00522</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.00979</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.005580000000000001</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>-0.00662</v>
+      </c>
+      <c r="O47" s="7" t="n">
+        <v>0.01335781080177645</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(Python で計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>FriS(候補)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.01402</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.03729</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.01328</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.01777</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.02775</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>-0.03414</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>-0.02158</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0.08554585015648009</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。それ以前は選抜がこの期間を見て決めた値なので、手法の証拠にはならない。</t>
-        </is>
+          <t>WedS(候補)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.008020000000000001</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.00455</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-0.01089</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-0.01569</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.00861</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.00375</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.00145</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.00434</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <v>0.0613420391284365</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>TueS(候補)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>-0.01366</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>-0.0008500000000000001</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.01023</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>-0.00601</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-0.01582</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0.00734</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0.009800326668017334</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Thu(候補)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.00329</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.01546</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.006770000000000001</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.01998</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-0.00298</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>-0.01638</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-0.00634</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.03244</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>0.00447</v>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>0.05896529488595936</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N46">
+  <conditionalFormatting sqref="C5:N51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -11322,22 +13368,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2021 年(全 42 セル)</t>
+          <t>紙上フォワード 月次リターン 2021 年(全 47 セル = 既存 42 + 候補 5)</t>
         </is>
       </c>
     </row>
@@ -11384,6 +13431,11 @@
           <t>活動月数</t>
         </is>
       </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>+月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -11411,6 +13463,9 @@
       <c r="G5" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H5" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -11438,6 +13493,9 @@
       <c r="G6" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H6" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -11465,6 +13523,9 @@
       <c r="G7" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H7" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -11492,6 +13553,9 @@
       <c r="G8" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H8" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -11519,6 +13583,9 @@
       <c r="G9" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H9" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -11546,6 +13613,9 @@
       <c r="G10" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H10" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -11573,6 +13643,9 @@
       <c r="G11" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H11" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -11600,6 +13673,9 @@
       <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H12" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -11627,6 +13703,9 @@
       <c r="G13" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -11654,6 +13733,9 @@
       <c r="G14" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H14" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -11681,6 +13763,9 @@
       <c r="G15" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H15" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -11708,6 +13793,9 @@
       <c r="G16" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H16" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -11735,6 +13823,9 @@
       <c r="G17" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H17" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -11762,6 +13853,9 @@
       <c r="G18" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H18" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -11789,6 +13883,9 @@
       <c r="G19" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H19" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -11816,6 +13913,9 @@
       <c r="G20" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H20" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -11843,6 +13943,9 @@
       <c r="G21" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H21" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -11870,6 +13973,9 @@
       <c r="G22" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H22" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -11897,6 +14003,9 @@
       <c r="G23" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -11924,6 +14033,9 @@
       <c r="G24" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -11951,6 +14063,9 @@
       <c r="G25" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H25" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -11978,6 +14093,9 @@
       <c r="G26" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H26" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -12005,6 +14123,9 @@
       <c r="G27" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -12032,6 +14153,9 @@
       <c r="G28" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -12059,6 +14183,9 @@
       <c r="G29" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H29" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -12082,6 +14209,9 @@
       </c>
       <c r="G30" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -12099,6 +14229,9 @@
       <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -12120,6 +14253,9 @@
       <c r="G32" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -12141,6 +14277,9 @@
       <c r="G33" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="H33" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -12165,6 +14304,9 @@
       <c r="G34" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="H34" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -12186,6 +14328,9 @@
       <c r="G35" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -12211,6 +14356,9 @@
         <v>0.01301123248582403</v>
       </c>
       <c r="G36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12229,6 +14377,9 @@
       <c r="G37" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -12253,6 +14404,9 @@
       <c r="G38" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="H38" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -12280,6 +14434,9 @@
       <c r="G39" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -12307,6 +14464,9 @@
       <c r="G40" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H40" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -12334,6 +14494,9 @@
       <c r="G41" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H41" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -12361,6 +14524,9 @@
       <c r="G42" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -12388,6 +14554,9 @@
       <c r="G43" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H43" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -12415,6 +14584,9 @@
       <c r="G44" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H44" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -12442,6 +14614,9 @@
       <c r="G45" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H45" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -12469,30 +14644,183 @@
       <c r="G46" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="H46" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MonS(候補)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0.006914165932220273</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(Python で計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>FriS(候補)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>-0.00711</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.00801</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.01763</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0.0184879118521073</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。それ以前は選抜がこの期間を見て決めた値なので、手法の証拠にはならない。</t>
-        </is>
+          <t>WedS(候補)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.008659999999999999</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.004759999999999999</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0.01597460542956797</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>TueS(候補)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>-0.00663</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.00219</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>-0.00469</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>-0.00912362800260702</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Thu(候補)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>-0.00147</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.01354</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0.01996432795228409</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:E46">
+  <conditionalFormatting sqref="C5:E51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -12514,10 +14842,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL50"/>
+  <dimension ref="A1:BM55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -12581,6 +14909,7 @@
     <col width="9" customWidth="1" min="62" max="62"/>
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
+    <col width="9" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12918,6 +15247,11 @@
           <t>活動月数</t>
         </is>
       </c>
+      <c r="BM4" s="3" t="inlineStr">
+        <is>
+          <t>+月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -13116,6 +15450,9 @@
       <c r="BL5" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM5" s="4" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -13314,6 +15651,9 @@
       <c r="BL6" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM6" s="4" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -13512,6 +15852,9 @@
       <c r="BL7" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM7" s="4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -13710,6 +16053,9 @@
       <c r="BL8" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM8" s="4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -13908,6 +16254,9 @@
       <c r="BL9" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM9" s="4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -14106,6 +16455,9 @@
       <c r="BL10" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM10" s="4" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -14304,6 +16656,9 @@
       <c r="BL11" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM11" s="4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -14499,6 +16854,9 @@
       <c r="BL12" s="4" t="n">
         <v>59</v>
       </c>
+      <c r="BM12" s="4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -14694,6 +17052,9 @@
       <c r="BL13" s="4" t="n">
         <v>59</v>
       </c>
+      <c r="BM13" s="4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -14892,6 +17253,9 @@
       <c r="BL14" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM14" s="4" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -15090,6 +17454,9 @@
       <c r="BL15" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM15" s="4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -15288,6 +17655,9 @@
       <c r="BL16" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM16" s="4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -15486,6 +17856,9 @@
       <c r="BL17" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM17" s="4" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -15684,6 +18057,9 @@
       <c r="BL18" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM18" s="4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -15882,6 +18258,9 @@
       <c r="BL19" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM19" s="4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -16080,6 +18459,9 @@
       <c r="BL20" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM20" s="4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -16278,6 +18660,9 @@
       <c r="BL21" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM21" s="4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -16476,6 +18861,9 @@
       <c r="BL22" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM22" s="4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -16674,6 +19062,9 @@
       <c r="BL23" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM23" s="4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -16872,6 +19263,9 @@
       <c r="BL24" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM24" s="4" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -17070,6 +19464,9 @@
       <c r="BL25" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM25" s="4" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -17268,6 +19665,9 @@
       <c r="BL26" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM26" s="4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -17466,6 +19866,9 @@
       <c r="BL27" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM27" s="4" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -17664,6 +20067,9 @@
       <c r="BL28" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM28" s="4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -17862,6 +20268,9 @@
       <c r="BL29" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM29" s="4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -17961,6 +20370,9 @@
       <c r="BL30" s="4" t="n">
         <v>27</v>
       </c>
+      <c r="BM30" s="4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -18069,6 +20481,9 @@
       <c r="BL31" s="4" t="n">
         <v>30</v>
       </c>
+      <c r="BM31" s="4" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -18186,6 +20601,9 @@
       <c r="BL32" s="4" t="n">
         <v>33</v>
       </c>
+      <c r="BM32" s="4" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -18288,6 +20706,9 @@
       <c r="BL33" s="4" t="n">
         <v>28</v>
       </c>
+      <c r="BM33" s="4" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -18387,6 +20808,9 @@
       <c r="BL34" s="4" t="n">
         <v>27</v>
       </c>
+      <c r="BM34" s="4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -18435,6 +20859,9 @@
       <c r="BL35" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="BM35" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -18558,6 +20985,9 @@
       <c r="BL36" s="4" t="n">
         <v>35</v>
       </c>
+      <c r="BM36" s="4" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -18648,6 +21078,9 @@
       <c r="BL37" s="4" t="n">
         <v>24</v>
       </c>
+      <c r="BM37" s="4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -18765,6 +21198,9 @@
       <c r="BL38" s="4" t="n">
         <v>33</v>
       </c>
+      <c r="BM38" s="4" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -18963,6 +21399,9 @@
       <c r="BL39" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM39" s="4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -19161,6 +21600,9 @@
       <c r="BL40" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM40" s="4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -19359,6 +21801,9 @@
       <c r="BL41" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM41" s="4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -19557,6 +22002,9 @@
       <c r="BL42" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM42" s="4" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -19755,6 +22203,9 @@
       <c r="BL43" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM43" s="4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -19902,6 +22353,9 @@
       <c r="BL44" s="4" t="n">
         <v>43</v>
       </c>
+      <c r="BM44" s="4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -20100,6 +22554,9 @@
       <c r="BL45" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM45" s="4" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -20298,30 +22755,1038 @@
       <c r="BL46" s="4" t="n">
         <v>60</v>
       </c>
+      <c r="BM46" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MonS(候補)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>-0.00351</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.006690000000000001</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.01342</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.009649999999999999</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-0.01016</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>-0.00019</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.00522</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.00979</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0.005580000000000001</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>-0.00662</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>-0.00834</v>
+      </c>
+      <c r="S47" s="5" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="U47" s="5" t="n">
+        <v>0.00461</v>
+      </c>
+      <c r="V47" s="5" t="n">
+        <v>0.00454</v>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>-0.008960000000000001</v>
+      </c>
+      <c r="X47" s="5" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>0.00483</v>
+      </c>
+      <c r="Z47" s="5" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AA47" s="5" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="AB47" s="5" t="n">
+        <v>0.00514</v>
+      </c>
+      <c r="AC47" s="5" t="n">
+        <v>-0.00736</v>
+      </c>
+      <c r="AD47" s="5" t="n">
+        <v>0.00436</v>
+      </c>
+      <c r="AE47" s="5" t="n">
+        <v>-0.00342</v>
+      </c>
+      <c r="AF47" s="5" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="AG47" s="5" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="AH47" s="5" t="n">
+        <v>0.005620000000000001</v>
+      </c>
+      <c r="AI47" s="5" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="AJ47" s="5" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="AK47" s="5" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="AL47" s="5" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="AM47" s="5" t="n">
+        <v>-0.00092</v>
+      </c>
+      <c r="AN47" s="5" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="AO47" s="5" t="n">
+        <v>0.006889999999999999</v>
+      </c>
+      <c r="AP47" s="5" t="n">
+        <v>0.00205</v>
+      </c>
+      <c r="AQ47" s="5" t="n">
+        <v>0.00508</v>
+      </c>
+      <c r="AR47" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AS47" s="5" t="n">
+        <v>0.00532</v>
+      </c>
+      <c r="AT47" s="5" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="AU47" s="5" t="n">
+        <v>-0.00661</v>
+      </c>
+      <c r="AV47" s="5" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="AW47" s="5" t="n">
+        <v>0.00727</v>
+      </c>
+      <c r="AX47" s="5" t="n">
+        <v>0.0005899999999999999</v>
+      </c>
+      <c r="AY47" s="5" t="n">
+        <v>0.006959999999999999</v>
+      </c>
+      <c r="AZ47" s="5" t="n">
+        <v>0.00466</v>
+      </c>
+      <c r="BA47" s="5" t="n">
+        <v>0.0007099999999999999</v>
+      </c>
+      <c r="BB47" s="5" t="n">
+        <v>0.008239999999999999</v>
+      </c>
+      <c r="BC47" s="5" t="n">
+        <v>0.00422</v>
+      </c>
+      <c r="BD47" s="5" t="n">
+        <v>0.00834</v>
+      </c>
+      <c r="BE47" s="5" t="n">
+        <v>0.00303</v>
+      </c>
+      <c r="BF47" s="5" t="n">
+        <v>0.00731</v>
+      </c>
+      <c r="BG47" s="5" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="BH47" s="5" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="BI47" s="6" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="BJ47" s="6" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="BK47" s="7" t="n">
+        <v>0.1560937305392334</v>
+      </c>
+      <c r="BL47" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM47" s="4" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(Python で計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>FriS(候補)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>-0.00711</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.00801</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.01763</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.01402</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0.03729</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.01328</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.01777</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0.02775</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>-0.03414</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>-0.02158</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>-0.03353</v>
+      </c>
+      <c r="S48" s="5" t="n">
+        <v>0.03909</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>-0.00478</v>
+      </c>
+      <c r="U48" s="5" t="n">
+        <v>0.01759</v>
+      </c>
+      <c r="V48" s="5" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="W48" s="5" t="n">
+        <v>-0.00784</v>
+      </c>
+      <c r="X48" s="5" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="Y48" s="5" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="Z48" s="5" t="n">
+        <v>-0.005330000000000001</v>
+      </c>
+      <c r="AA48" s="5" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="AB48" s="5" t="n">
+        <v>-0.02624</v>
+      </c>
+      <c r="AC48" s="5" t="n">
+        <v>-0.00282</v>
+      </c>
+      <c r="AD48" s="5" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="AE48" s="5" t="n">
+        <v>0.00559</v>
+      </c>
+      <c r="AF48" s="5" t="n">
+        <v>0.01206</v>
+      </c>
+      <c r="AG48" s="5" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="AH48" s="5" t="n">
+        <v>-0.01399</v>
+      </c>
+      <c r="AI48" s="5" t="n">
+        <v>0.01936</v>
+      </c>
+      <c r="AJ48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="5" t="n">
+        <v>-0.02186</v>
+      </c>
+      <c r="AL48" s="5" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="AM48" s="5" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="AN48" s="5" t="n">
+        <v>0.00353</v>
+      </c>
+      <c r="AO48" s="5" t="n">
+        <v>0.00198</v>
+      </c>
+      <c r="AP48" s="5" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="AQ48" s="5" t="n">
+        <v>0.00394</v>
+      </c>
+      <c r="AR48" s="5" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="AS48" s="5" t="n">
+        <v>0.03224</v>
+      </c>
+      <c r="AT48" s="5" t="n">
+        <v>-0.02547</v>
+      </c>
+      <c r="AU48" s="5" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="AV48" s="5" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="AW48" s="5" t="n">
+        <v>-0.01047</v>
+      </c>
+      <c r="AX48" s="5" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="AY48" s="5" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="AZ48" s="5" t="n">
+        <v>-0.00616</v>
+      </c>
+      <c r="BA48" s="5" t="n">
+        <v>0.00473</v>
+      </c>
+      <c r="BB48" s="5" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="BC48" s="5" t="n">
+        <v>-0.01551</v>
+      </c>
+      <c r="BD48" s="5" t="n">
+        <v>0.03045</v>
+      </c>
+      <c r="BE48" s="5" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="BF48" s="5" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="BG48" s="5" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="BH48" s="5" t="n">
+        <v>-0.00644</v>
+      </c>
+      <c r="BI48" s="6" t="n">
+        <v>-0.006979999999999999</v>
+      </c>
+      <c r="BJ48" s="6" t="n">
+        <v>-0.00075</v>
+      </c>
+      <c r="BK48" s="7" t="n">
+        <v>0.296223760871984</v>
+      </c>
+      <c r="BL48" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM48" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。それ以前は選抜がこの期間を見て決めた値なので、手法の証拠にはならない。</t>
-        </is>
+          <t>WedS(候補)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.008659999999999999</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.004759999999999999</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.008020000000000001</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.00455</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>-0.01089</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.01569</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.00861</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-0.00375</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.00145</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0.00434</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>0.00493</v>
+      </c>
+      <c r="S49" s="5" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="T49" s="5" t="n">
+        <v>-0.00156</v>
+      </c>
+      <c r="U49" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="V49" s="5" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="W49" s="5" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="X49" s="5" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="Y49" s="5" t="n">
+        <v>0.00165</v>
+      </c>
+      <c r="Z49" s="5" t="n">
+        <v>-0.00993</v>
+      </c>
+      <c r="AA49" s="5" t="n">
+        <v>0.01959</v>
+      </c>
+      <c r="AB49" s="5" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="AC49" s="5" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="AD49" s="5" t="n">
+        <v>0.01775</v>
+      </c>
+      <c r="AE49" s="5" t="n">
+        <v>-0.00183</v>
+      </c>
+      <c r="AF49" s="5" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="AG49" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="AH49" s="5" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="AI49" s="5" t="n">
+        <v>0.00149</v>
+      </c>
+      <c r="AJ49" s="5" t="n">
+        <v>0.02143</v>
+      </c>
+      <c r="AK49" s="5" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="AL49" s="5" t="n">
+        <v>-0.01226</v>
+      </c>
+      <c r="AM49" s="5" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="AN49" s="5" t="n">
+        <v>-0.00526</v>
+      </c>
+      <c r="AO49" s="5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="AP49" s="5" t="n">
+        <v>0.00061</v>
+      </c>
+      <c r="AQ49" s="5" t="n">
+        <v>0.008619999999999999</v>
+      </c>
+      <c r="AR49" s="5" t="n">
+        <v>-0.005759999999999999</v>
+      </c>
+      <c r="AS49" s="5" t="n">
+        <v>-0.02502</v>
+      </c>
+      <c r="AT49" s="5" t="n">
+        <v>0.00506</v>
+      </c>
+      <c r="AU49" s="5" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="AV49" s="5" t="n">
+        <v>-0.00324</v>
+      </c>
+      <c r="AW49" s="5" t="n">
+        <v>0.004670000000000001</v>
+      </c>
+      <c r="AX49" s="5" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="AY49" s="5" t="n">
+        <v>-0.005390000000000001</v>
+      </c>
+      <c r="AZ49" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="BA49" s="5" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="BB49" s="5" t="n">
+        <v>-0.01076</v>
+      </c>
+      <c r="BC49" s="5" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="BD49" s="5" t="n">
+        <v>-0.00745</v>
+      </c>
+      <c r="BE49" s="5" t="n">
+        <v>-0.006690000000000001</v>
+      </c>
+      <c r="BF49" s="5" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="BG49" s="5" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="BH49" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="BI49" s="6" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="BJ49" s="6" t="n">
+        <v>-0.00369</v>
+      </c>
+      <c r="BK49" s="7" t="n">
+        <v>0.1912640779995847</v>
+      </c>
+      <c r="BL49" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM49" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>TueS(候補)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>-0.00663</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.00219</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>-0.00469</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.01366</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0008500000000000001</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.01023</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>-0.00601</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>-0.01582</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>0.00734</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="S50" s="5" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>-0.00707</v>
+      </c>
+      <c r="U50" s="5" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="V50" s="5" t="n">
+        <v>0.00451</v>
+      </c>
+      <c r="W50" s="5" t="n">
+        <v>0.00078</v>
+      </c>
+      <c r="X50" s="5" t="n">
+        <v>0.00984</v>
+      </c>
+      <c r="Y50" s="5" t="n">
+        <v>0.00895</v>
+      </c>
+      <c r="Z50" s="5" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="AA50" s="5" t="n">
+        <v>0.00049</v>
+      </c>
+      <c r="AB50" s="5" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="AC50" s="5" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="AD50" s="5" t="n">
+        <v>-0.009769999999999999</v>
+      </c>
+      <c r="AE50" s="5" t="n">
+        <v>0.00017</v>
+      </c>
+      <c r="AF50" s="5" t="n">
+        <v>0.00204</v>
+      </c>
+      <c r="AG50" s="5" t="n">
+        <v>-0.00258</v>
+      </c>
+      <c r="AH50" s="5" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="AI50" s="5" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="AJ50" s="5" t="n">
+        <v>0.00249</v>
+      </c>
+      <c r="AK50" s="5" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="AL50" s="5" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="AM50" s="5" t="n">
+        <v>-0.00715</v>
+      </c>
+      <c r="AN50" s="5" t="n">
+        <v>-0.00532</v>
+      </c>
+      <c r="AO50" s="5" t="n">
+        <v>-0.00112</v>
+      </c>
+      <c r="AP50" s="5" t="n">
+        <v>0.00309</v>
+      </c>
+      <c r="AQ50" s="5" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="AR50" s="5" t="n">
+        <v>0.00167</v>
+      </c>
+      <c r="AS50" s="5" t="n">
+        <v>-0.01268</v>
+      </c>
+      <c r="AT50" s="5" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="AU50" s="5" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="AV50" s="5" t="n">
+        <v>0.005719999999999999</v>
+      </c>
+      <c r="AW50" s="5" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="AX50" s="5" t="n">
+        <v>0.00818</v>
+      </c>
+      <c r="AY50" s="5" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="AZ50" s="5" t="n">
+        <v>-0.00231</v>
+      </c>
+      <c r="BA50" s="5" t="n">
+        <v>-0.0003500000000000001</v>
+      </c>
+      <c r="BB50" s="5" t="n">
+        <v>0.01317</v>
+      </c>
+      <c r="BC50" s="5" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="BD50" s="5" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="BE50" s="5" t="n">
+        <v>0.00615</v>
+      </c>
+      <c r="BF50" s="5" t="n">
+        <v>-0.00477</v>
+      </c>
+      <c r="BG50" s="5" t="n">
+        <v>0.00102</v>
+      </c>
+      <c r="BH50" s="5" t="n">
+        <v>-0.00604</v>
+      </c>
+      <c r="BI50" s="6" t="n">
+        <v>0.00194</v>
+      </c>
+      <c r="BJ50" s="6" t="n">
+        <v>-0.00333</v>
+      </c>
+      <c r="BK50" s="7" t="n">
+        <v>0.1028789181132783</v>
+      </c>
+      <c r="BL50" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM50" s="4" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Thu(候補)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>-0.00147</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.01354</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.00329</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.01546</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-0.006770000000000001</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.01998</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>-0.00298</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>-0.01638</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>-0.00634</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>0.03244</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>0.00447</v>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>-0.00289</v>
+      </c>
+      <c r="S51" s="5" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="T51" s="5" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="U51" s="5" t="n">
+        <v>-0.00248</v>
+      </c>
+      <c r="V51" s="5" t="n">
+        <v>-0.00577</v>
+      </c>
+      <c r="W51" s="5" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="X51" s="5" t="n">
+        <v>-0.00641</v>
+      </c>
+      <c r="Y51" s="5" t="n">
+        <v>-0.00359</v>
+      </c>
+      <c r="Z51" s="5" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="AA51" s="5" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="AB51" s="5" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="AC51" s="5" t="n">
+        <v>0.00713</v>
+      </c>
+      <c r="AD51" s="5" t="n">
+        <v>0.01318</v>
+      </c>
+      <c r="AE51" s="5" t="n">
+        <v>0.01418</v>
+      </c>
+      <c r="AF51" s="5" t="n">
+        <v>0.01405</v>
+      </c>
+      <c r="AG51" s="5" t="n">
+        <v>0.02761</v>
+      </c>
+      <c r="AH51" s="5" t="n">
+        <v>0.0005600000000000001</v>
+      </c>
+      <c r="AI51" s="5" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="AJ51" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AK51" s="5" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="AL51" s="5" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="AM51" s="5" t="n">
+        <v>0.01429</v>
+      </c>
+      <c r="AN51" s="5" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="AO51" s="5" t="n">
+        <v>-0.02198</v>
+      </c>
+      <c r="AP51" s="5" t="n">
+        <v>0.03668</v>
+      </c>
+      <c r="AQ51" s="5" t="n">
+        <v>-0.01188</v>
+      </c>
+      <c r="AR51" s="5" t="n">
+        <v>0.02773</v>
+      </c>
+      <c r="AS51" s="5" t="n">
+        <v>0.03561</v>
+      </c>
+      <c r="AT51" s="5" t="n">
+        <v>-0.00506</v>
+      </c>
+      <c r="AU51" s="5" t="n">
+        <v>0.00595</v>
+      </c>
+      <c r="AV51" s="5" t="n">
+        <v>-0.00086</v>
+      </c>
+      <c r="AW51" s="5" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="AX51" s="5" t="n">
+        <v>0.02009</v>
+      </c>
+      <c r="AY51" s="5" t="n">
+        <v>0.05052</v>
+      </c>
+      <c r="AZ51" s="5" t="n">
+        <v>-0.01719</v>
+      </c>
+      <c r="BA51" s="5" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="BB51" s="5" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="BC51" s="5" t="n">
+        <v>-0.06426</v>
+      </c>
+      <c r="BD51" s="5" t="n">
+        <v>-0.03804</v>
+      </c>
+      <c r="BE51" s="5" t="n">
+        <v>-0.01259</v>
+      </c>
+      <c r="BF51" s="5" t="n">
+        <v>-0.00094</v>
+      </c>
+      <c r="BG51" s="5" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="BH51" s="5" t="n">
+        <v>0.01981</v>
+      </c>
+      <c r="BI51" s="6" t="n">
+        <v>-0.01494</v>
+      </c>
+      <c r="BJ51" s="6" t="n">
+        <v>-0.01183</v>
+      </c>
+      <c r="BK51" s="7" t="n">
+        <v>0.4469399803594707</v>
+      </c>
+      <c r="BL51" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM51" s="4" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:BJ46">
+  <conditionalFormatting sqref="C5:BJ51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/research/results/paper_forward_5y.xlsx
+++ b/research/results/paper_forward_5y.xlsx
@@ -57,7 +57,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +79,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDD9F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +109,7 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -470,11 +476,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -492,7 +498,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2026 年(全 47 セル = 既存 42 + 候補 5)</t>
+          <t>紙上フォワード 月次リターン 2026 年(全 55 セル = 既存 42 + 候補 5 + 時間帯 8)</t>
         </is>
       </c>
     </row>
@@ -2666,29 +2672,296 @@
         <v>3</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 16-20S</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>-0.00167</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.00796</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.01444</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>-0.00447</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.009350000000000001</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-0.008659999999999999</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>0.01359912484429593</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 00-04S</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.00814</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.00386</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-0.0005899999999999999</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.00326</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="L53" s="7" t="n">
+        <v>0.03219592914807778</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 16-20S</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>-0.01024</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.00855</v>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>0.03937744029514745</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.00103</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>-0.01362</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>0.04352896081262791</v>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AUDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>-0.00115</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0.01129</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.00282</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.01252</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.009250000000000001</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>0.02857088660375173</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 20-00S</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 16-20S</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CHFJPY 20-00S</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済み。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑 = docs/229/230 の候補(日足・順位付け窓 2021-10〜2025-09)。紫 = docs/233/234 の時間帯セル S1〜S8(Dukascopy H1・月〜木 4h SHORT・往復 2pip・スワップ未反映・順位付け窓は 2021-10〜2025-08 / 2024-12)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>出所: research/forward/paper_forward.py + plusmonth_search_h1(Dukascopy)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。EURGBP/CHFJPY の時間帯セルは 2025-12 までのデータ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:K51">
+  <conditionalFormatting sqref="C5:K59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -2710,11 +2983,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -2735,7 +3008,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2025 年(全 47 セル = 既存 42 + 候補 5)</t>
+          <t>紙上フォワード 月次リターン 2025 年(全 55 セル = 既存 42 + 候補 5 + 時間帯 8)</t>
         </is>
       </c>
     </row>
@@ -5305,29 +5578,485 @@
         <v>8</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 16-20S</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.00714</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.00363</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>-0.007980000000000001</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.00612</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.00096</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.00668</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.00367</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0.00284</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0.00461</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0.00449</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>0.04598974465455585</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 00-04S</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.00149</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.00404</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.01924</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.00067</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-0.00052</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.005390000000000001</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="O53" s="7" t="n">
+        <v>0.08452505392616128</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 16-20S</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>-0.00103</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>-0.00621</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-0.0007000000000000001</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.00133</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0.01095</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0.06590082467500125</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.00213</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.01691</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.009439999999999999</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>-0.00458</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>-0.00113</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.00286</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.008659999999999999</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.00455</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="O55" s="7" t="n">
+        <v>0.05897553272733935</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AUDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0.00517</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.008189999999999999</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.00674</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-0.00128</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0.00187</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0.00456</v>
+      </c>
+      <c r="O56" s="7" t="n">
+        <v>0.03693020671889924</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 20-00S</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.00384</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>-0.0006900000000000001</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.00054</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>-0.00343</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.00592</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>0.02930015180319256</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 16-20S</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>0.008409999999999999</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>-0.00313</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0.00288</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0.00392</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0.07945459531028609</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CHFJPY 20-00S</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0.004670000000000001</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-0.00024</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.00396</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.00791</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.00424</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.00256</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.00374</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="O59" s="7" t="n">
+        <v>0.06581520865744861</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済み。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑 = docs/229/230 の候補(日足・順位付け窓 2021-10〜2025-09)。紫 = docs/233/234 の時間帯セル S1〜S8(Dukascopy H1・月〜木 4h SHORT・往復 2pip・スワップ未反映・順位付け窓は 2021-10〜2025-08 / 2024-12)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>出所: research/forward/paper_forward.py + plusmonth_search_h1(Dukascopy)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。EURGBP/CHFJPY の時間帯セルは 2025-12 までのデータ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N51">
+  <conditionalFormatting sqref="C5:N59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -5349,11 +6078,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -5374,7 +6103,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2024 年(全 47 セル = 既存 42 + 候補 5)</t>
+          <t>紙上フォワード 月次リターン 2024 年(全 55 セル = 既存 42 + 候補 5 + 時間帯 8)</t>
         </is>
       </c>
     </row>
@@ -7965,29 +8694,485 @@
         <v>10</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 16-20S</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.007169999999999999</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.00553</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.00641</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.00398</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0.02022</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>-0.005849999999999999</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>0.06812574360743184</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 00-04S</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.00507</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.00561</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.00219</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.00221</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>-0.00779</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>-0.00431</v>
+      </c>
+      <c r="O53" s="7" t="n">
+        <v>0.02412588456332276</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 16-20S</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.0008100000000000001</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>-0.0007199999999999999</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.00419</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.00174</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.01197</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0.05564896249895313</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.0005899999999999999</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>-0.00415</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.00407</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.00364</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.00016</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.00437</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.00641</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="O55" s="7" t="n">
+        <v>0.06434543590091235</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AUDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>-0.00443</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.00148</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.00272</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.00362</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.004030000000000001</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="O56" s="7" t="n">
+        <v>0.04635386209207315</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 20-00S</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.00611</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.005350000000000001</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.00187</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.00312</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.00369</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.00309</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0.009340000000000001</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.005410000000000001</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>0.05302407049870417</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 16-20S</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.00193</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.00312</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.00446</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>-0.00383</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0.00615</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0.00176</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0.03665786401486737</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CHFJPY 20-00S</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>-0.00106</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>-0.00246</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.00954</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.008970000000000001</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.00485</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.00504</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0.00431</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="O59" s="7" t="n">
+        <v>0.03582294925136198</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済み。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑 = docs/229/230 の候補(日足・順位付け窓 2021-10〜2025-09)。紫 = docs/233/234 の時間帯セル S1〜S8(Dukascopy H1・月〜木 4h SHORT・往復 2pip・スワップ未反映・順位付け窓は 2021-10〜2025-08 / 2024-12)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>出所: research/forward/paper_forward.py + plusmonth_search_h1(Dukascopy)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。EURGBP/CHFJPY の時間帯セルは 2025-12 までのデータ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N51">
+  <conditionalFormatting sqref="C5:N59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -8009,11 +9194,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -8034,7 +9219,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2023 年(全 47 セル = 既存 42 + 候補 5)</t>
+          <t>紙上フォワード 月次リターン 2023 年(全 55 セル = 既存 42 + 候補 5 + 時間帯 8)</t>
         </is>
       </c>
     </row>
@@ -10637,29 +11822,485 @@
         <v>6</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 16-20S</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.00133</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.00817</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>-0.0008799999999999999</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>-0.00715</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0.01187</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>-0.00202</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0.00602</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>0.05837220639591645</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 00-04S</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.00826</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.00987</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-0.00048</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.00478</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.00205</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.01208</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="O53" s="7" t="n">
+        <v>0.08029553308620829</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 16-20S</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>-0.00424</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.005370000000000001</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.00443</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>-0.00225</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0.03803203382545695</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.01672</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.005809999999999999</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.008460000000000001</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.01853</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.00526</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="O55" s="7" t="n">
+        <v>0.08666143703205043</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AUDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>-0.00347</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.00224</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.00881</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.005520000000000001</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.00707</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0.00483</v>
+      </c>
+      <c r="O56" s="7" t="n">
+        <v>0.04873248793833174</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 20-00S</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.00196</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.00199</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.00206</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.00491</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>0.0280983553723495</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 16-20S</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>-0.00242</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.01038</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.005639999999999999</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.00181</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.00455</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.008319999999999999</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0.00688</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.0006400000000000001</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0.00561</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0.05916333512843575</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CHFJPY 20-00S</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.01299</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.008449999999999999</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.00687</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.00174</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="O59" s="7" t="n">
+        <v>0.06497027988252779</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済み。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑 = docs/229/230 の候補(日足・順位付け窓 2021-10〜2025-09)。紫 = docs/233/234 の時間帯セル S1〜S8(Dukascopy H1・月〜木 4h SHORT・往復 2pip・スワップ未反映・順位付け窓は 2021-10〜2025-08 / 2024-12)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>出所: research/forward/paper_forward.py + plusmonth_search_h1(Dukascopy)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。EURGBP/CHFJPY の時間帯セルは 2025-12 までのデータ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N51">
+  <conditionalFormatting sqref="C5:N59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -10681,11 +12322,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -10706,7 +12347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2022 年(全 47 セル = 既存 42 + 候補 5)</t>
+          <t>紙上フォワード 月次リターン 2022 年(全 55 セル = 既存 42 + 候補 5 + 時間帯 8)</t>
         </is>
       </c>
     </row>
@@ -13324,29 +14965,485 @@
         <v>8</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 16-20S</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.006730000000000001</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>-0.00394</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>-0.007039999999999999</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.00031</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.00929</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>-0.00202</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>-0.00282</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0.00976</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>-0.00244</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>0.02959089151468408</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 00-04S</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>-0.00348</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>-0.00217</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.00384</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.00745</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="O53" s="7" t="n">
+        <v>0.02681489884405419</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 16-20S</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.00168</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.01042</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>-0.00373</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.00831</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0.05846288788991871</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.01184</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.01053</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.01175</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.006790000000000001</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.02241</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>-0.00297</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-0.00831</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.008319999999999999</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="O55" s="7" t="n">
+        <v>0.09972390847492774</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AUDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.00619</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.00826</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.00822</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.00629</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0.00392</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>-0.00457</v>
+      </c>
+      <c r="O56" s="7" t="n">
+        <v>0.07768072488456501</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 20-00S</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.00411</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.005659999999999999</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.004719999999999999</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.00295</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.01561</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.00222</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>0.06106003869510279</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 16-20S</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>-0.00065</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.01036</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.00078</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.01529</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>-0.00501</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0.03545040081591067</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CHFJPY 20-00S</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>-0.00195</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-0.01203</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-0.00135</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.00214</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>-0.005390000000000001</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.00117</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>-0.00469</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="O59" s="7" t="n">
+        <v>0.0003935094953695373</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済み。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑 = docs/229/230 の候補(日足・順位付け窓 2021-10〜2025-09)。紫 = docs/233/234 の時間帯セル S1〜S8(Dukascopy H1・月〜木 4h SHORT・往復 2pip・スワップ未反映・順位付け窓は 2021-10〜2025-08 / 2024-12)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>出所: research/forward/paper_forward.py + plusmonth_search_h1(Dukascopy)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。EURGBP/CHFJPY の時間帯セルは 2025-12 までのデータ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:N51">
+  <conditionalFormatting sqref="C5:N59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -13368,11 +15465,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -13384,7 +15481,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紙上フォワード 月次リターン 2021 年(全 47 セル = 既存 42 + 候補 5)</t>
+          <t>紙上フォワード 月次リターン 2021 年(全 55 セル = 既存 42 + 候補 5 + 時間帯 8)</t>
         </is>
       </c>
     </row>
@@ -14798,29 +16895,269 @@
         <v>2</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 16-20S</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.01407</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>0.02849093046382389</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 00-04S</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.00338</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>-0.00127</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>0.00491160338071972</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 16-20S</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.0007099999999999999</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.00559</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0.01546133501698987</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.006959999999999999</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.00188</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>0.01412938643350414</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AUDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.00903</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0.0003500000000000001</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.00651</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0.01595424487485508</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 20-00S</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.00499</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.00628</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.00131</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0.01262614195173217</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 16-20S</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>0.00531</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.003505912695957791</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CHFJPY 20-00S</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>-0.00267</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.00024</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>-0.002151321379423865</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済み。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑 = docs/229/230 の候補(日足・順位付け窓 2021-10〜2025-09)。紫 = docs/233/234 の時間帯セル S1〜S8(Dukascopy H1・月〜木 4h SHORT・往復 2pip・スワップ未反映・順位付け窓は 2021-10〜2025-08 / 2024-12)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>出所: research/forward/paper_forward.py + plusmonth_search_h1(Dukascopy)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。EURGBP/CHFJPY の時間帯セルは 2025-12 までのデータ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:E51">
+  <conditionalFormatting sqref="C5:E59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -14842,11 +17179,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM55"/>
+  <dimension ref="A1:BM63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -23764,29 +26101,1526 @@
         <v>37</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 16-20S</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.01407</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.006730000000000001</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-0.00394</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-0.007039999999999999</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.00031</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0.00929</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>-0.00202</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>-0.00282</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0.00976</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>-0.00244</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="S52" s="5" t="n">
+        <v>0.00133</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U52" s="5" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="V52" s="5" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>0.00817</v>
+      </c>
+      <c r="X52" s="5" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>-0.0008799999999999999</v>
+      </c>
+      <c r="Z52" s="5" t="n">
+        <v>-0.00715</v>
+      </c>
+      <c r="AA52" s="5" t="n">
+        <v>0.01187</v>
+      </c>
+      <c r="AB52" s="5" t="n">
+        <v>-0.00202</v>
+      </c>
+      <c r="AC52" s="5" t="n">
+        <v>0.00602</v>
+      </c>
+      <c r="AD52" s="5" t="n">
+        <v>0.007169999999999999</v>
+      </c>
+      <c r="AE52" s="5" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="AF52" s="5" t="n">
+        <v>0.00553</v>
+      </c>
+      <c r="AG52" s="5" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="AH52" s="5" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AI52" s="5" t="n">
+        <v>0.00641</v>
+      </c>
+      <c r="AJ52" s="5" t="n">
+        <v>0.00398</v>
+      </c>
+      <c r="AK52" s="5" t="n">
+        <v>0.02022</v>
+      </c>
+      <c r="AL52" s="5" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="AM52" s="5" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="AN52" s="5" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="AO52" s="5" t="n">
+        <v>-0.005849999999999999</v>
+      </c>
+      <c r="AP52" s="5" t="n">
+        <v>0.00714</v>
+      </c>
+      <c r="AQ52" s="5" t="n">
+        <v>0.00363</v>
+      </c>
+      <c r="AR52" s="5" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="AS52" s="5" t="n">
+        <v>-0.007980000000000001</v>
+      </c>
+      <c r="AT52" s="5" t="n">
+        <v>0.00612</v>
+      </c>
+      <c r="AU52" s="5" t="n">
+        <v>0.00096</v>
+      </c>
+      <c r="AV52" s="5" t="n">
+        <v>0.00668</v>
+      </c>
+      <c r="AW52" s="5" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AX52" s="5" t="n">
+        <v>0.00367</v>
+      </c>
+      <c r="AY52" s="5" t="n">
+        <v>0.00284</v>
+      </c>
+      <c r="AZ52" s="5" t="n">
+        <v>0.00461</v>
+      </c>
+      <c r="BA52" s="5" t="n">
+        <v>0.00449</v>
+      </c>
+      <c r="BB52" s="5" t="n">
+        <v>-0.00167</v>
+      </c>
+      <c r="BC52" s="5" t="n">
+        <v>0.00796</v>
+      </c>
+      <c r="BD52" s="5" t="n">
+        <v>0.01444</v>
+      </c>
+      <c r="BE52" s="5" t="n">
+        <v>-0.00447</v>
+      </c>
+      <c r="BF52" s="5" t="n">
+        <v>0.009350000000000001</v>
+      </c>
+      <c r="BG52" s="5" t="n">
+        <v>-0.008659999999999999</v>
+      </c>
+      <c r="BH52" s="5" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="BK52" s="7" t="n">
+        <v>0.2691694813693584</v>
+      </c>
+      <c r="BL52" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="BM52" s="4" t="n">
+        <v>42</v>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>累積 = Π(1+月次)−1(計算済みの値。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>USDCHF 00-04S</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.00338</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>-0.00127</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-0.00348</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-0.00217</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.00384</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>-0.00745</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>0.00826</v>
+      </c>
+      <c r="S53" s="5" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="T53" s="5" t="n">
+        <v>0.00987</v>
+      </c>
+      <c r="U53" s="5" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="V53" s="5" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="W53" s="5" t="n">
+        <v>-0.00048</v>
+      </c>
+      <c r="X53" s="5" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="Y53" s="5" t="n">
+        <v>0.00478</v>
+      </c>
+      <c r="Z53" s="5" t="n">
+        <v>0.00205</v>
+      </c>
+      <c r="AA53" s="5" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="AB53" s="5" t="n">
+        <v>0.01208</v>
+      </c>
+      <c r="AC53" s="5" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="AD53" s="5" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="AE53" s="5" t="n">
+        <v>0.00507</v>
+      </c>
+      <c r="AF53" s="5" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="AG53" s="5" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="AH53" s="5" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="AI53" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="AJ53" s="5" t="n">
+        <v>0.00561</v>
+      </c>
+      <c r="AK53" s="5" t="n">
+        <v>0.00219</v>
+      </c>
+      <c r="AL53" s="5" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="AM53" s="5" t="n">
+        <v>0.00221</v>
+      </c>
+      <c r="AN53" s="5" t="n">
+        <v>-0.00779</v>
+      </c>
+      <c r="AO53" s="5" t="n">
+        <v>-0.00431</v>
+      </c>
+      <c r="AP53" s="5" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="AQ53" s="5" t="n">
+        <v>0.00149</v>
+      </c>
+      <c r="AR53" s="5" t="n">
+        <v>0.00404</v>
+      </c>
+      <c r="AS53" s="5" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="AT53" s="5" t="n">
+        <v>0.01924</v>
+      </c>
+      <c r="AU53" s="5" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="AV53" s="5" t="n">
+        <v>0.00067</v>
+      </c>
+      <c r="AW53" s="5" t="n">
+        <v>-0.00052</v>
+      </c>
+      <c r="AX53" s="5" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="AY53" s="5" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="AZ53" s="5" t="n">
+        <v>0.005390000000000001</v>
+      </c>
+      <c r="BA53" s="5" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="BB53" s="5" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="BC53" s="5" t="n">
+        <v>0.00814</v>
+      </c>
+      <c r="BD53" s="5" t="n">
+        <v>0.00386</v>
+      </c>
+      <c r="BE53" s="5" t="n">
+        <v>-0.0005899999999999999</v>
+      </c>
+      <c r="BF53" s="5" t="n">
+        <v>-0.00326</v>
+      </c>
+      <c r="BG53" s="5" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="BH53" s="5" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="BK53" s="7" t="n">
+        <v>0.2779612249162158</v>
+      </c>
+      <c r="BL53" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="BM53" s="4" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑の行 = docs/229/230 の候補 5 本(探索で見つけたもの。順位付け窓 2021-10〜2025-09、2025-10 以降がサンプル外)。</t>
-        </is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 16-20S</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.0007099999999999999</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.00559</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.00168</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-0.01042</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.00373</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0.00831</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>-0.00424</v>
+      </c>
+      <c r="S54" s="5" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="U54" s="5" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="V54" s="5" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="W54" s="5" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="X54" s="5" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="Y54" s="5" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="Z54" s="5" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="AA54" s="5" t="n">
+        <v>-0.005370000000000001</v>
+      </c>
+      <c r="AB54" s="5" t="n">
+        <v>0.00443</v>
+      </c>
+      <c r="AC54" s="5" t="n">
+        <v>-0.00225</v>
+      </c>
+      <c r="AD54" s="5" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="AE54" s="5" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="AF54" s="5" t="n">
+        <v>0.0008100000000000001</v>
+      </c>
+      <c r="AG54" s="5" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="AH54" s="5" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AI54" s="5" t="n">
+        <v>-0.0007199999999999999</v>
+      </c>
+      <c r="AJ54" s="5" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="AK54" s="5" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AL54" s="5" t="n">
+        <v>-0.00419</v>
+      </c>
+      <c r="AM54" s="5" t="n">
+        <v>-0.00174</v>
+      </c>
+      <c r="AN54" s="5" t="n">
+        <v>0.01197</v>
+      </c>
+      <c r="AO54" s="5" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="AP54" s="5" t="n">
+        <v>-0.00103</v>
+      </c>
+      <c r="AQ54" s="5" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="AR54" s="5" t="n">
+        <v>-0.00621</v>
+      </c>
+      <c r="AS54" s="5" t="n">
+        <v>-0.0007000000000000001</v>
+      </c>
+      <c r="AT54" s="5" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="AU54" s="5" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="AV54" s="5" t="n">
+        <v>0.00133</v>
+      </c>
+      <c r="AW54" s="5" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="AX54" s="5" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AY54" s="5" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="AZ54" s="5" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="BA54" s="5" t="n">
+        <v>0.01095</v>
+      </c>
+      <c r="BB54" s="5" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="BC54" s="5" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="BD54" s="5" t="n">
+        <v>-0.01024</v>
+      </c>
+      <c r="BE54" s="5" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="BF54" s="5" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="BG54" s="5" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="BH54" s="5" t="n">
+        <v>0.00855</v>
+      </c>
+      <c r="BK54" s="7" t="n">
+        <v>0.3048464032076992</v>
+      </c>
+      <c r="BL54" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="BM54" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>出所: research/forward/paper_forward.py(Yahoo 日足・コスト = モデル定数 往復 2pip / 相対コスト)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。</t>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NZDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.006959999999999999</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.00188</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.01184</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.01053</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.01175</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.006790000000000001</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.02241</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>-0.00297</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>-0.00831</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>0.008319999999999999</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>0.01672</v>
+      </c>
+      <c r="S55" s="5" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="T55" s="5" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="U55" s="5" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="V55" s="5" t="n">
+        <v>0.005809999999999999</v>
+      </c>
+      <c r="W55" s="5" t="n">
+        <v>0.008460000000000001</v>
+      </c>
+      <c r="X55" s="5" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="Y55" s="5" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="Z55" s="5" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AA55" s="5" t="n">
+        <v>0.01853</v>
+      </c>
+      <c r="AB55" s="5" t="n">
+        <v>0.00526</v>
+      </c>
+      <c r="AC55" s="5" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="AD55" s="5" t="n">
+        <v>0.0005899999999999999</v>
+      </c>
+      <c r="AE55" s="5" t="n">
+        <v>-0.00415</v>
+      </c>
+      <c r="AF55" s="5" t="n">
+        <v>0.00407</v>
+      </c>
+      <c r="AG55" s="5" t="n">
+        <v>0.00364</v>
+      </c>
+      <c r="AH55" s="5" t="n">
+        <v>0.00016</v>
+      </c>
+      <c r="AI55" s="5" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="AJ55" s="5" t="n">
+        <v>0.00437</v>
+      </c>
+      <c r="AK55" s="5" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="AL55" s="5" t="n">
+        <v>0.00641</v>
+      </c>
+      <c r="AM55" s="5" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="AN55" s="5" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="AO55" s="5" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="AP55" s="5" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="AQ55" s="5" t="n">
+        <v>0.00213</v>
+      </c>
+      <c r="AR55" s="5" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="AS55" s="5" t="n">
+        <v>0.01691</v>
+      </c>
+      <c r="AT55" s="5" t="n">
+        <v>0.009439999999999999</v>
+      </c>
+      <c r="AU55" s="5" t="n">
+        <v>-0.00458</v>
+      </c>
+      <c r="AV55" s="5" t="n">
+        <v>-0.00113</v>
+      </c>
+      <c r="AW55" s="5" t="n">
+        <v>-0.00286</v>
+      </c>
+      <c r="AX55" s="5" t="n">
+        <v>0.008659999999999999</v>
+      </c>
+      <c r="AY55" s="5" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="AZ55" s="5" t="n">
+        <v>0.00455</v>
+      </c>
+      <c r="BA55" s="5" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="BB55" s="5" t="n">
+        <v>0.00103</v>
+      </c>
+      <c r="BC55" s="5" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="BD55" s="5" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="BE55" s="5" t="n">
+        <v>-0.01362</v>
+      </c>
+      <c r="BF55" s="5" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="BG55" s="5" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="BH55" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="BK55" s="7" t="n">
+        <v>0.4254248450400802</v>
+      </c>
+      <c r="BL55" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="BM55" s="4" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AUDUSD 20-00S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.00903</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0.0003500000000000001</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.00651</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.00619</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.00826</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.00822</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0.00629</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>0.00392</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>-0.00457</v>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="S56" s="5" t="n">
+        <v>-0.00347</v>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="U56" s="5" t="n">
+        <v>-0.00224</v>
+      </c>
+      <c r="V56" s="5" t="n">
+        <v>0.00881</v>
+      </c>
+      <c r="W56" s="5" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="X56" s="5" t="n">
+        <v>0.005520000000000001</v>
+      </c>
+      <c r="Y56" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="Z56" s="5" t="n">
+        <v>0.00707</v>
+      </c>
+      <c r="AA56" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="AB56" s="5" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="AC56" s="5" t="n">
+        <v>0.00483</v>
+      </c>
+      <c r="AD56" s="5" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="AE56" s="5" t="n">
+        <v>-0.00443</v>
+      </c>
+      <c r="AF56" s="5" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="AG56" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="AH56" s="5" t="n">
+        <v>0.00148</v>
+      </c>
+      <c r="AI56" s="5" t="n">
+        <v>0.00272</v>
+      </c>
+      <c r="AJ56" s="5" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="AK56" s="5" t="n">
+        <v>0.00362</v>
+      </c>
+      <c r="AL56" s="5" t="n">
+        <v>0.004030000000000001</v>
+      </c>
+      <c r="AM56" s="5" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="AN56" s="5" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="AO56" s="5" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="AP56" s="5" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="AQ56" s="5" t="n">
+        <v>0.00517</v>
+      </c>
+      <c r="AR56" s="5" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="AS56" s="5" t="n">
+        <v>0.008189999999999999</v>
+      </c>
+      <c r="AT56" s="5" t="n">
+        <v>0.00674</v>
+      </c>
+      <c r="AU56" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="AV56" s="5" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AW56" s="5" t="n">
+        <v>-0.00128</v>
+      </c>
+      <c r="AX56" s="5" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="AY56" s="5" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AZ56" s="5" t="n">
+        <v>0.00187</v>
+      </c>
+      <c r="BA56" s="5" t="n">
+        <v>0.00456</v>
+      </c>
+      <c r="BB56" s="5" t="n">
+        <v>-0.00115</v>
+      </c>
+      <c r="BC56" s="5" t="n">
+        <v>0.01129</v>
+      </c>
+      <c r="BD56" s="5" t="n">
+        <v>0.00282</v>
+      </c>
+      <c r="BE56" s="5" t="n">
+        <v>-0.01252</v>
+      </c>
+      <c r="BF56" s="5" t="n">
+        <v>0.009250000000000001</v>
+      </c>
+      <c r="BG56" s="5" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="BH56" s="5" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="BK56" s="7" t="n">
+        <v>0.2814194796021992</v>
+      </c>
+      <c r="BL56" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="BM56" s="4" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 20-00S</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.00499</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.00628</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.00131</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.00411</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.005659999999999999</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.004719999999999999</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.00295</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.01561</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="Q57" s="5" t="n">
+        <v>0.00222</v>
+      </c>
+      <c r="R57" s="5" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="S57" s="5" t="n">
+        <v>0.00196</v>
+      </c>
+      <c r="T57" s="5" t="n">
+        <v>0.00199</v>
+      </c>
+      <c r="U57" s="5" t="n">
+        <v>0.00206</v>
+      </c>
+      <c r="V57" s="5" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="W57" s="5" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="X57" s="5" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="Y57" s="5" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="Z57" s="5" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="AA57" s="5" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="AB57" s="5" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="AC57" s="5" t="n">
+        <v>0.00491</v>
+      </c>
+      <c r="AD57" s="5" t="n">
+        <v>0.00611</v>
+      </c>
+      <c r="AE57" s="5" t="n">
+        <v>0.005350000000000001</v>
+      </c>
+      <c r="AF57" s="5" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="AG57" s="5" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="AH57" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="AI57" s="5" t="n">
+        <v>0.00187</v>
+      </c>
+      <c r="AJ57" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="AK57" s="5" t="n">
+        <v>0.00312</v>
+      </c>
+      <c r="AL57" s="5" t="n">
+        <v>0.00369</v>
+      </c>
+      <c r="AM57" s="5" t="n">
+        <v>0.00309</v>
+      </c>
+      <c r="AN57" s="5" t="n">
+        <v>0.009340000000000001</v>
+      </c>
+      <c r="AO57" s="5" t="n">
+        <v>0.005410000000000001</v>
+      </c>
+      <c r="AP57" s="5" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="AQ57" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="AR57" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="AS57" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AT57" s="5" t="n">
+        <v>0.00384</v>
+      </c>
+      <c r="AU57" s="5" t="n">
+        <v>-0.0006900000000000001</v>
+      </c>
+      <c r="AV57" s="5" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="AW57" s="5" t="n">
+        <v>0.00054</v>
+      </c>
+      <c r="AX57" s="5" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="AY57" s="5" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="AZ57" s="5" t="n">
+        <v>-0.00343</v>
+      </c>
+      <c r="BA57" s="5" t="n">
+        <v>0.00592</v>
+      </c>
+      <c r="BK57" s="7" t="n">
+        <v>0.1973030625195504</v>
+      </c>
+      <c r="BL57" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="BM57" s="4" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>EURGBP 16-20S</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>0.00531</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>-0.00065</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.01036</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0.00078</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0.01529</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>-0.00501</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="S58" s="5" t="n">
+        <v>-0.00242</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0.01038</v>
+      </c>
+      <c r="U58" s="5" t="n">
+        <v>0.005639999999999999</v>
+      </c>
+      <c r="V58" s="5" t="n">
+        <v>0.00181</v>
+      </c>
+      <c r="W58" s="5" t="n">
+        <v>0.00455</v>
+      </c>
+      <c r="X58" s="5" t="n">
+        <v>0.008319999999999999</v>
+      </c>
+      <c r="Y58" s="5" t="n">
+        <v>0.00688</v>
+      </c>
+      <c r="Z58" s="5" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="AA58" s="5" t="n">
+        <v>-0.0006400000000000001</v>
+      </c>
+      <c r="AB58" s="5" t="n">
+        <v>0.00561</v>
+      </c>
+      <c r="AC58" s="5" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="AD58" s="5" t="n">
+        <v>0.00193</v>
+      </c>
+      <c r="AE58" s="5" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="AF58" s="5" t="n">
+        <v>0.00312</v>
+      </c>
+      <c r="AG58" s="5" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="AH58" s="5" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="AI58" s="5" t="n">
+        <v>0.00446</v>
+      </c>
+      <c r="AJ58" s="5" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="AK58" s="5" t="n">
+        <v>-0.00383</v>
+      </c>
+      <c r="AL58" s="5" t="n">
+        <v>0.00615</v>
+      </c>
+      <c r="AM58" s="5" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="AN58" s="5" t="n">
+        <v>0.00176</v>
+      </c>
+      <c r="AO58" s="5" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="AP58" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="AQ58" s="5" t="n">
+        <v>0.008409999999999999</v>
+      </c>
+      <c r="AR58" s="5" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="AS58" s="5" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="AT58" s="5" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="AU58" s="5" t="n">
+        <v>-0.00313</v>
+      </c>
+      <c r="AV58" s="5" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="AW58" s="5" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="AX58" s="5" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="AY58" s="5" t="n">
+        <v>0.00288</v>
+      </c>
+      <c r="AZ58" s="5" t="n">
+        <v>0.00392</v>
+      </c>
+      <c r="BA58" s="5" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="BK58" s="7" t="n">
+        <v>0.2315498645123859</v>
+      </c>
+      <c r="BL58" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="BM58" s="4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Sess(候補)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CHFJPY 20-00S</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>-0.00267</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.00024</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-0.00195</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>-0.01203</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>-0.00135</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.00214</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>-0.005390000000000001</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.00117</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>-0.00469</v>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="Q59" s="5" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="R59" s="5" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="S59" s="5" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="U59" s="5" t="n">
+        <v>0.01299</v>
+      </c>
+      <c r="V59" s="5" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="W59" s="5" t="n">
+        <v>0.008449999999999999</v>
+      </c>
+      <c r="X59" s="5" t="n">
+        <v>0.00687</v>
+      </c>
+      <c r="Y59" s="5" t="n">
+        <v>0.00174</v>
+      </c>
+      <c r="Z59" s="5" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="AA59" s="5" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="AB59" s="5" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="AC59" s="5" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="AD59" s="5" t="n">
+        <v>-0.00106</v>
+      </c>
+      <c r="AE59" s="5" t="n">
+        <v>-0.00246</v>
+      </c>
+      <c r="AF59" s="5" t="n">
+        <v>0.00954</v>
+      </c>
+      <c r="AG59" s="5" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="AH59" s="5" t="n">
+        <v>0.008970000000000001</v>
+      </c>
+      <c r="AI59" s="5" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AJ59" s="5" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="AK59" s="5" t="n">
+        <v>-0.00485</v>
+      </c>
+      <c r="AL59" s="5" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="AM59" s="5" t="n">
+        <v>0.00504</v>
+      </c>
+      <c r="AN59" s="5" t="n">
+        <v>0.00431</v>
+      </c>
+      <c r="AO59" s="5" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AP59" s="5" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="AQ59" s="5" t="n">
+        <v>0.004670000000000001</v>
+      </c>
+      <c r="AR59" s="5" t="n">
+        <v>-0.00024</v>
+      </c>
+      <c r="AS59" s="5" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="AT59" s="5" t="n">
+        <v>0.00396</v>
+      </c>
+      <c r="AU59" s="5" t="n">
+        <v>0.00791</v>
+      </c>
+      <c r="AV59" s="5" t="n">
+        <v>0.00424</v>
+      </c>
+      <c r="AW59" s="5" t="n">
+        <v>0.00256</v>
+      </c>
+      <c r="AX59" s="5" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="AY59" s="5" t="n">
+        <v>0.00374</v>
+      </c>
+      <c r="AZ59" s="5" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="BA59" s="5" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="BK59" s="7" t="n">
+        <v>0.1736550775455648</v>
+      </c>
+      <c r="BL59" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="BM59" s="4" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>累積 = Π(1+月次)−1(計算済み。空欄 = その月に活動なし)。v4 の空欄はシグナル無しであって損益 0 ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>黄色 = 選抜凍結(2026-07-29)後のサンプル外。緑 = docs/229/230 の候補(日足・順位付け窓 2021-10〜2025-09)。紫 = docs/233/234 の時間帯セル S1〜S8(Dukascopy H1・月〜木 4h SHORT・往復 2pip・スワップ未反映・順位付け窓は 2021-10〜2025-08 / 2024-12)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>出所: research/forward/paper_forward.py + plusmonth_search_h1(Dukascopy)。実口座の成績ではない。口座への効き方 = 値 × 重み × 倍率。EURGBP/CHFJPY の時間帯セルは 2025-12 までのデータ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:BJ51">
+  <conditionalFormatting sqref="C5:BJ59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
